--- a/data/trans_orig/IP1022_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP1022_2023-Edad-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>346</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5552</t>
+          <t>4359</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>638</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7748</t>
+          <t>7229</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1833</t>
+          <t>1994</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9286</t>
+          <t>9632</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>8,14%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>51351</t>
+          <t>52544</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>56544</t>
+          <t>56557</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>53696</t>
+          <t>54215</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>60545</t>
+          <t>60806</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>109061</t>
+          <t>108715</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>116514</t>
+          <t>116353</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,31%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4064</t>
+          <t>4455</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13000</t>
+          <t>13418</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6273</t>
+          <t>5763</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17546</t>
+          <t>16299</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12285</t>
+          <t>12424</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27084</t>
+          <t>26325</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,7%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>146299</t>
+          <t>145881</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>155235</t>
+          <t>154844</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>165008</t>
+          <t>166255</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>176281</t>
+          <t>176791</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>91,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>314769</t>
+          <t>315528</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>329568</t>
+          <t>329429</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,37%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4127</t>
+          <t>4554</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13933</t>
+          <t>14721</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10103</t>
+          <t>10357</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25485</t>
+          <t>25596</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16384</t>
+          <t>17387</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33780</t>
+          <t>34993</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>9,08%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>159139</t>
+          <t>158351</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>168945</t>
+          <t>168518</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>187005</t>
+          <t>186894</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>202387</t>
+          <t>202133</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>351783</t>
+          <t>350570</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>369179</t>
+          <t>368176</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,49%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16089</t>
+          <t>16430</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>43553</t>
+          <t>43884</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17503</t>
+          <t>18113</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>45267</t>
+          <t>45663</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>39205</t>
+          <t>38658</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>78517</t>
+          <t>79321</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,75%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>231905</t>
+          <t>231574</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>259369</t>
+          <t>259028</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,19%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>255980</t>
+          <t>255584</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>283744</t>
+          <t>283134</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>498188</t>
+          <t>497384</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>537500</t>
+          <t>538047</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,3%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>31503</t>
+          <t>32300</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>62818</t>
+          <t>64667</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>45454</t>
+          <t>44031</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>79980</t>
+          <t>78467</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>83732</t>
+          <t>83249</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>130841</t>
+          <t>130132</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,15%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>601914</t>
+          <t>600065</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>633229</t>
+          <t>632432</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>677756</t>
+          <t>679269</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>712282</t>
+          <t>713705</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1291627</t>
+          <t>1292336</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1338736</t>
+          <t>1339219</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,15%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP1022_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP1022_2023-Edad-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2629</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>680</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6238</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>5,2%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>12,34%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1562</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>346</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4359</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,75%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>7,66%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3116</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>263</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7229</t>
+          <t>3835</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>4679</t>
+          <t>3931</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1994</t>
+          <t>1681</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9632</t>
+          <t>8056</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>7,9%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>47908</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>44299</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>49857</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>94,8%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>87,66%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>98,66%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>105</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>55341</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>52544</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>56557</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>97,25%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>92,34%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>99,39%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>58328</t>
+          <t>50118</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>54215</t>
+          <t>47585</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>60806</t>
+          <t>51157</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>113668</t>
+          <t>98026</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>108715</t>
+          <t>93901</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>116353</t>
+          <t>100276</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,35%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>108</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>56903</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>56903</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>56903</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>51420</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>51420</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>51420</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>118347</t>
+          <t>101957</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>118347</t>
+          <t>101957</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>118347</t>
+          <t>101957</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>8469</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>5145</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>13463</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>5,38%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3,27%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>8,55%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>7726</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>4455</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>13418</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>4,85%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2,8%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>8,42%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>10389</t>
+          <t>7655</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5763</t>
+          <t>4332</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16299</t>
+          <t>12520</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>18116</t>
+          <t>16124</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12424</t>
+          <t>10500</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26325</t>
+          <t>22652</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,47%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>149053</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>144059</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>152377</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>94,62%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>91,45%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>96,73%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>245</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>151573</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>145881</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>154844</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>95,15%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>91,58%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>97,2%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>260</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>172165</t>
+          <t>137863</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>166255</t>
+          <t>132998</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>176791</t>
+          <t>141186</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>323737</t>
+          <t>286915</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>315528</t>
+          <t>280387</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>329429</t>
+          <t>292539</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,54%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>276</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>15728</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9317</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>25346</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>7,86%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>4,66%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>12,67%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>8220</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>4554</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>14721</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>4,75%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,63%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>8,51%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>16561</t>
+          <t>8806</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10357</t>
+          <t>4768</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25596</t>
+          <t>15128</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>24781</t>
+          <t>24534</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17387</t>
+          <t>16721</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34993</t>
+          <t>34881</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,31%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>184398</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>174780</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>190809</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>92,14%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>87,33%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>95,34%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>222</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>164852</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>158351</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>168518</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>95,25%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>91,49%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>97,37%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>195929</t>
+          <t>165866</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>186894</t>
+          <t>159544</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>202133</t>
+          <t>169904</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>360782</t>
+          <t>350264</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>350570</t>
+          <t>339917</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>368176</t>
+          <t>358077</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,54%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>26296</t>
+          <t>22200</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16430</t>
+          <t>15122</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>43884</t>
+          <t>32347</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>27561</t>
+          <t>22543</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18113</t>
+          <t>14790</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>45663</t>
+          <t>31283</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>53857</t>
+          <t>44744</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>38658</t>
+          <t>33632</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>79321</t>
+          <t>57306</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>10,52%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>311</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>266075</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>255928</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>273153</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>92,3%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>88,78%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>94,75%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>312</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>249162</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>231574</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>259028</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>90,45%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>84,07%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>94,04%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>311</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>273686</t>
+          <t>234010</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>255584</t>
+          <t>225270</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>283134</t>
+          <t>241763</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>522848</t>
+          <t>500084</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>497384</t>
+          <t>487522</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>538047</t>
+          <t>511196</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,83%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>288275</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>288275</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>288275</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>342</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>275458</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>275458</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>275458</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>341</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>301247</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>301247</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>301247</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>576705</t>
+          <t>544828</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>576705</t>
+          <t>544828</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>576705</t>
+          <t>544828</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>49026</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>38275</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>63224</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>7,04%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>5,5%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>9,08%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>43804</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>32300</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>64667</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>6,59%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>4,86%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>9,73%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>57628</t>
+          <t>40307</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>44031</t>
+          <t>30744</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>78467</t>
+          <t>52096</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>101432</t>
+          <t>89332</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>83249</t>
+          <t>74610</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>130132</t>
+          <t>106578</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>8,05%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>908</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>647434</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>633236</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>658185</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>92,96%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>90,92%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>94,5%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>884</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>620928</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>600065</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>632432</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>93,41%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>90,27%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>95,14%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>908</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>700108</t>
+          <t>587856</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>679269</t>
+          <t>576067</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>713705</t>
+          <t>597419</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1321036</t>
+          <t>1235291</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1292336</t>
+          <t>1218045</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1339219</t>
+          <t>1250013</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,37%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>696460</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>696460</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>696460</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>941</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>664732</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>664732</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>664732</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>976</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>757736</t>
+          <t>628163</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>757736</t>
+          <t>628163</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>757736</t>
+          <t>628163</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1422468</t>
+          <t>1324623</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1422468</t>
+          <t>1324623</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1422468</t>
+          <t>1324623</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
